--- a/AAII_Financials/Quarterly/MTCPY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MTCPY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="92">
   <si>
     <t>MTCPY</t>
   </si>
@@ -656,7 +656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:O102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="1"/>
@@ -671,61 +671,76 @@
     <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -765,8 +780,20 @@
       <c r="O8" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S8" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -806,8 +833,20 @@
       <c r="O9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -847,8 +886,20 @@
       <c r="O10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -864,8 +915,12 @@
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -905,8 +960,20 @@
       <c r="O12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -946,8 +1013,20 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -987,8 +1066,20 @@
       <c r="O14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S14" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,8 +1119,20 @@
       <c r="O15" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S15" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1042,8 +1145,12 @@
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
-    </row>
-    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1083,8 +1190,20 @@
       <c r="O17" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S17" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1124,8 +1243,20 @@
       <c r="O18" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S18" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1141,8 +1272,12 @@
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
-    </row>
-    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1182,8 +1317,20 @@
       <c r="O20" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S20" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1223,8 +1370,20 @@
       <c r="O21" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S21" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1264,8 +1423,20 @@
       <c r="O22" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S22" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1305,8 +1476,20 @@
       <c r="O23" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R23" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S23" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1346,8 +1529,20 @@
       <c r="O24" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S24" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1387,8 +1582,20 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1428,8 +1635,20 @@
       <c r="O26" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S26" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1469,8 +1688,20 @@
       <c r="O27" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R27" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S27" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1510,8 +1741,20 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1551,8 +1794,20 @@
       <c r="O29" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S29" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1592,8 +1847,20 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1633,8 +1900,20 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1674,8 +1953,20 @@
       <c r="O32" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R32" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S32" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1715,8 +2006,20 @@
       <c r="O33" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S33" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1756,8 +2059,20 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1797,54 +2112,78 @@
       <c r="O35" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R35" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S35" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1860,8 +2199,12 @@
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
-    </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1877,377 +2220,489 @@
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
-    </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7850300</v>
+      </c>
+      <c r="E41" s="3">
+        <v>7852400</v>
+      </c>
+      <c r="F41" s="3">
+        <v>4960300</v>
+      </c>
+      <c r="G41" s="3">
+        <v>4962100</v>
+      </c>
+      <c r="H41" s="3">
         <v>6530100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="I41" s="3">
         <v>6588700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="J41" s="3">
         <v>2811200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="K41" s="3">
         <v>2810500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="L41" s="3">
         <v>3158800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="M41" s="3">
         <v>3151700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="N41" s="3">
         <v>1993800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="O41" s="3">
         <v>1988900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="P41" s="3">
         <v>2399100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="Q41" s="3">
         <v>2394900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="R41" s="3">
         <v>1313400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="S41" s="3">
         <v>1304600</v>
       </c>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>38800</v>
+      </c>
+      <c r="E42" s="3">
+        <v>38800</v>
+      </c>
+      <c r="F42" s="3">
+        <v>131800</v>
+      </c>
+      <c r="G42" s="3">
+        <v>131900</v>
+      </c>
+      <c r="H42" s="3">
         <v>94000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="I42" s="3">
         <v>94900</v>
       </c>
-      <c r="F42" s="3">
+      <c r="J42" s="3">
         <v>50600</v>
       </c>
-      <c r="G42" s="3">
+      <c r="K42" s="3">
         <v>50600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="L42" s="3">
         <v>22700</v>
       </c>
-      <c r="I42" s="3">
+      <c r="M42" s="3">
         <v>22600</v>
       </c>
-      <c r="J42" s="3">
+      <c r="N42" s="3">
         <v>24600</v>
       </c>
-      <c r="K42" s="3">
+      <c r="O42" s="3">
         <v>24500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="P42" s="3">
         <v>26500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="Q42" s="3">
         <v>26500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="R42" s="3">
         <v>244800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="S42" s="3">
         <v>243200</v>
       </c>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2788800</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2789500</v>
+      </c>
+      <c r="F43" s="3">
+        <v>2062500</v>
+      </c>
+      <c r="G43" s="3">
+        <v>2063200</v>
+      </c>
+      <c r="H43" s="3">
         <v>2348300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="I43" s="3">
         <v>2369400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="J43" s="3">
         <v>2397800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="K43" s="3">
         <v>2397200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="L43" s="3">
         <v>2635500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="M43" s="3">
         <v>2629600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="N43" s="3">
         <v>2149900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="O43" s="3">
         <v>2144700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="P43" s="3">
         <v>2393900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="Q43" s="3">
         <v>2389800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="R43" s="3">
         <v>2120000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="S43" s="3">
         <v>2105700</v>
       </c>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>945300</v>
+      </c>
+      <c r="E44" s="3">
+        <v>945500</v>
+      </c>
+      <c r="F44" s="3">
+        <v>755800</v>
+      </c>
+      <c r="G44" s="3">
+        <v>756100</v>
+      </c>
+      <c r="H44" s="3">
         <v>641900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="I44" s="3">
         <v>647700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="J44" s="3">
         <v>623500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="K44" s="3">
         <v>623300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="L44" s="3">
         <v>692000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="M44" s="3">
         <v>690400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="N44" s="3">
         <v>575500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="O44" s="3">
         <v>574100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="P44" s="3">
         <v>577400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="Q44" s="3">
         <v>576400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="R44" s="3">
         <v>532100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="S44" s="3">
         <v>528500</v>
       </c>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6925200</v>
+      </c>
+      <c r="E45" s="3">
+        <v>6927000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>826500</v>
+      </c>
+      <c r="G45" s="3">
+        <v>826800</v>
+      </c>
+      <c r="H45" s="3">
         <v>803600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="I45" s="3">
         <v>810800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="J45" s="3">
         <v>791100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="K45" s="3">
         <v>790900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="L45" s="3">
         <v>851300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="M45" s="3">
         <v>849400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="N45" s="3">
         <v>944500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="O45" s="3">
         <v>942200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="P45" s="3">
         <v>662800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="Q45" s="3">
         <v>661700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="R45" s="3">
         <v>545700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="S45" s="3">
         <v>542000</v>
       </c>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>18548300</v>
+      </c>
+      <c r="E46" s="3">
+        <v>18553200</v>
+      </c>
+      <c r="F46" s="3">
+        <v>8736900</v>
+      </c>
+      <c r="G46" s="3">
+        <v>8740000</v>
+      </c>
+      <c r="H46" s="3">
         <v>10417900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="I46" s="3">
         <v>10511300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="J46" s="3">
         <v>6674200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="K46" s="3">
         <v>6672500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="L46" s="3">
         <v>7360300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="M46" s="3">
         <v>7343700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="N46" s="3">
         <v>5688300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="O46" s="3">
         <v>5674500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="P46" s="3">
         <v>6059800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="Q46" s="3">
         <v>6049300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="R46" s="3">
         <v>4756000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="S46" s="3">
         <v>4724100</v>
       </c>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>4132600</v>
+      </c>
+      <c r="E47" s="3">
+        <v>4133600</v>
+      </c>
+      <c r="F47" s="3">
+        <v>2666700</v>
+      </c>
+      <c r="G47" s="3">
+        <v>2667600</v>
+      </c>
+      <c r="H47" s="3">
         <v>2583800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="I47" s="3">
         <v>2607000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="J47" s="3">
         <v>1911200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="K47" s="3">
         <v>1910700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="L47" s="3">
         <v>1784600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="M47" s="3">
         <v>1780600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="N47" s="3">
         <v>1743000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="O47" s="3">
         <v>1738800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="P47" s="3">
         <v>1692900</v>
       </c>
-      <c r="M47" s="3">
+      <c r="Q47" s="3">
         <v>1689900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="R47" s="3">
         <v>1698300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="S47" s="3">
         <v>1686900</v>
       </c>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>22716600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>22722600</v>
+      </c>
+      <c r="F48" s="3">
+        <v>22071900</v>
+      </c>
+      <c r="G48" s="3">
+        <v>22079800</v>
+      </c>
+      <c r="H48" s="3">
         <v>21157300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="I48" s="3">
         <v>21347000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="J48" s="3">
         <v>20714300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="K48" s="3">
         <v>20709100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="L48" s="3">
         <v>19698400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="M48" s="3">
         <v>19653900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="N48" s="3">
         <v>19163800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="O48" s="3">
         <v>19117400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="P48" s="3">
         <v>18525400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="Q48" s="3">
         <v>18493500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="R48" s="3">
         <v>18412300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="S48" s="3">
         <v>18288800</v>
       </c>
     </row>
-    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5367800</v>
+      </c>
+      <c r="E49" s="3">
+        <v>5369200</v>
+      </c>
+      <c r="F49" s="3">
+        <v>5352500</v>
+      </c>
+      <c r="G49" s="3">
+        <v>5354400</v>
+      </c>
+      <c r="H49" s="3">
         <v>5102800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="I49" s="3">
         <v>5148600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="J49" s="3">
         <v>5105100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="K49" s="3">
         <v>5103800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="L49" s="3">
         <v>4746800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="M49" s="3">
         <v>4736000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="N49" s="3">
         <v>4700600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="O49" s="3">
         <v>4689200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="P49" s="3">
         <v>4567400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="Q49" s="3">
         <v>4559500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="R49" s="3">
         <v>4563600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="S49" s="3">
         <v>4533000</v>
       </c>
     </row>
-    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2287,8 +2742,20 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2328,49 +2795,73 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11936000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>11939100</v>
+      </c>
+      <c r="F52" s="3">
+        <v>12343600</v>
+      </c>
+      <c r="G52" s="3">
+        <v>12348100</v>
+      </c>
+      <c r="H52" s="3">
         <v>11946600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="I52" s="3">
         <v>12053700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="J52" s="3">
         <v>12832300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="K52" s="3">
         <v>12829100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="L52" s="3">
         <v>12497500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="M52" s="3">
         <v>12469300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="N52" s="3">
         <v>12925000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="O52" s="3">
         <v>12893700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="P52" s="3">
         <v>12433200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="Q52" s="3">
         <v>12411800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="R52" s="3">
         <v>12114300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="S52" s="3">
         <v>12033100</v>
       </c>
     </row>
-    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2410,49 +2901,73 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>62781400</v>
+      </c>
+      <c r="E54" s="3">
+        <v>62797800</v>
+      </c>
+      <c r="F54" s="3">
+        <v>51254700</v>
+      </c>
+      <c r="G54" s="3">
+        <v>51273100</v>
+      </c>
+      <c r="H54" s="3">
         <v>51286600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="I54" s="3">
         <v>51746400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="J54" s="3">
         <v>47312400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="K54" s="3">
         <v>47300500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="L54" s="3">
         <v>46235300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="M54" s="3">
         <v>46130800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="N54" s="3">
         <v>44346200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="O54" s="3">
         <v>44238800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="P54" s="3">
         <v>43607400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="Q54" s="3">
         <v>43532200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="R54" s="3">
         <v>41948000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="S54" s="3">
         <v>41666600</v>
       </c>
     </row>
-    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2468,8 +2983,12 @@
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
-    </row>
-    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2485,254 +3004,330 @@
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
-    </row>
-    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2272700</v>
+      </c>
+      <c r="E57" s="3">
+        <v>2273300</v>
+      </c>
+      <c r="F57" s="3">
+        <v>2133900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>2134700</v>
+      </c>
+      <c r="H57" s="3">
         <v>2242300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="I57" s="3">
         <v>2262400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="J57" s="3">
         <v>2315900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="K57" s="3">
         <v>2315400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="L57" s="3">
         <v>2107500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="M57" s="3">
         <v>2102800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="N57" s="3">
         <v>2149300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="O57" s="3">
         <v>2144100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="P57" s="3">
         <v>2031500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="Q57" s="3">
         <v>2028000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="R57" s="3">
         <v>1998800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="S57" s="3">
         <v>1985400</v>
       </c>
     </row>
-    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>76800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>76800</v>
+      </c>
+      <c r="F58" s="3">
+        <v>164600</v>
+      </c>
+      <c r="G58" s="3">
+        <v>164600</v>
+      </c>
+      <c r="H58" s="3">
         <v>137200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="I58" s="3">
         <v>138400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="J58" s="3">
         <v>548300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="K58" s="3">
         <v>548200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="L58" s="3">
         <v>151900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="M58" s="3">
         <v>151500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="N58" s="3">
         <v>263700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="O58" s="3">
         <v>263100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="P58" s="3">
         <v>244900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="Q58" s="3">
         <v>244500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="R58" s="3">
         <v>504400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="S58" s="3">
         <v>501000</v>
       </c>
     </row>
-    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>747400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>747600</v>
+      </c>
+      <c r="F59" s="3">
+        <v>891800</v>
+      </c>
+      <c r="G59" s="3">
+        <v>892100</v>
+      </c>
+      <c r="H59" s="3">
         <v>979400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="I59" s="3">
         <v>988200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="J59" s="3">
         <v>1026300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="K59" s="3">
         <v>1026100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="L59" s="3">
         <v>1403900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="M59" s="3">
         <v>1400700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="N59" s="3">
         <v>721000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="O59" s="3">
         <v>719200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="P59" s="3">
         <v>747400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="Q59" s="3">
         <v>746100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="R59" s="3">
         <v>556000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="S59" s="3">
         <v>552200</v>
       </c>
     </row>
-    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3096900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>3097700</v>
+      </c>
+      <c r="F60" s="3">
+        <v>3222400</v>
+      </c>
+      <c r="G60" s="3">
+        <v>3223500</v>
+      </c>
+      <c r="H60" s="3">
         <v>3385500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="I60" s="3">
         <v>3415900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="J60" s="3">
         <v>3905600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="K60" s="3">
         <v>3904700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="L60" s="3">
         <v>3679400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="M60" s="3">
         <v>3671100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="N60" s="3">
         <v>3150300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="O60" s="3">
         <v>3142700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="P60" s="3">
         <v>3567300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="Q60" s="3">
         <v>3561200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="R60" s="3">
         <v>3077700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="S60" s="3">
         <v>3057100</v>
       </c>
     </row>
-    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>21737500</v>
+      </c>
+      <c r="E61" s="3">
+        <v>21743200</v>
+      </c>
+      <c r="F61" s="3">
+        <v>11379000</v>
+      </c>
+      <c r="G61" s="3">
+        <v>11383100</v>
+      </c>
+      <c r="H61" s="3">
         <v>11755400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="I61" s="3">
         <v>11860800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="J61" s="3">
         <v>9469700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="K61" s="3">
         <v>9467300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="L61" s="3">
         <v>8905600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="M61" s="3">
         <v>8885500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="N61" s="3">
         <v>7408700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="O61" s="3">
         <v>7390800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="P61" s="3">
         <v>6578000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="Q61" s="3">
         <v>6566700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="R61" s="3">
         <v>5674000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="S61" s="3">
         <v>5636000</v>
       </c>
     </row>
-    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>5957300</v>
+      </c>
+      <c r="E62" s="3">
+        <v>5958900</v>
+      </c>
+      <c r="F62" s="3">
+        <v>6025200</v>
+      </c>
+      <c r="G62" s="3">
+        <v>6027400</v>
+      </c>
+      <c r="H62" s="3">
         <v>6526500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="I62" s="3">
         <v>6585100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="J62" s="3">
         <v>7198500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="K62" s="3">
         <v>7196600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="L62" s="3">
         <v>8041900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="M62" s="3">
         <v>8023700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="N62" s="3">
         <v>8300500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="O62" s="3">
         <v>8280400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="P62" s="3">
         <v>8363200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="Q62" s="3">
         <v>8348800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="R62" s="3">
         <v>7708200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="S62" s="3">
         <v>7656500</v>
       </c>
     </row>
-    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2772,8 +3367,20 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2813,8 +3420,20 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2854,49 +3473,73 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>33649200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>33657900</v>
+      </c>
+      <c r="F66" s="3">
+        <v>23452700</v>
+      </c>
+      <c r="G66" s="3">
+        <v>23461200</v>
+      </c>
+      <c r="H66" s="3">
         <v>24381000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="I66" s="3">
         <v>24599700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="J66" s="3">
         <v>23349300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="K66" s="3">
         <v>23343500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="L66" s="3">
         <v>23316800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="M66" s="3">
         <v>23264200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="N66" s="3">
         <v>21450700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="O66" s="3">
         <v>21398800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="P66" s="3">
         <v>20936200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="Q66" s="3">
         <v>20900100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="R66" s="3">
         <v>18874400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="S66" s="3">
         <v>18747800</v>
       </c>
     </row>
-    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2912,8 +3555,12 @@
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
-    </row>
-    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2953,8 +3600,20 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2994,8 +3653,20 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3035,8 +3706,20 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3076,49 +3759,73 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>17928000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>17932700</v>
+      </c>
+      <c r="F72" s="3">
+        <v>16724700</v>
+      </c>
+      <c r="G72" s="3">
+        <v>16730700</v>
+      </c>
+      <c r="H72" s="3">
         <v>16002300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="I72" s="3">
         <v>16145700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="J72" s="3">
         <v>15893700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="K72" s="3">
         <v>15889700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="L72" s="3">
         <v>14880900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="M72" s="3">
         <v>14847300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="N72" s="3">
         <v>14809300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="O72" s="3">
         <v>14773400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="P72" s="3">
         <v>14660200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="Q72" s="3">
         <v>14635000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="R72" s="3">
         <v>14906200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="S72" s="3">
         <v>14806200</v>
       </c>
     </row>
-    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3158,8 +3865,20 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3199,8 +3918,20 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3240,49 +3971,73 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>29044500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>29052100</v>
+      </c>
+      <c r="F76" s="3">
+        <v>27714100</v>
+      </c>
+      <c r="G76" s="3">
+        <v>27724000</v>
+      </c>
+      <c r="H76" s="3">
         <v>26821800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="I76" s="3">
         <v>27062300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="J76" s="3">
         <v>23897700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="K76" s="3">
         <v>23891700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="L76" s="3">
         <v>22841200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="M76" s="3">
         <v>22789600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="N76" s="3">
         <v>22829900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="O76" s="3">
         <v>22774600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="P76" s="3">
         <v>22605800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="Q76" s="3">
         <v>22566900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="R76" s="3">
         <v>22993300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="S76" s="3">
         <v>22839100</v>
       </c>
     </row>
-    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3322,54 +4077,78 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="G80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
     </row>
-    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3409,8 +4188,20 @@
       <c r="O81" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R81" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="S81" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3426,49 +4217,65 @@
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
-    </row>
-    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>186100</v>
+        <v>197400</v>
       </c>
       <c r="E83" s="3">
-        <v>185700</v>
+        <v>199200</v>
       </c>
       <c r="F83" s="3">
         <v>66000</v>
       </c>
       <c r="G83" s="3">
+        <v>66000</v>
+      </c>
+      <c r="H83" s="3">
+        <v>186100</v>
+      </c>
+      <c r="I83" s="3">
+        <v>185700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>66000</v>
+      </c>
+      <c r="K83" s="3">
         <v>65800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="L83" s="3">
         <v>194300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="M83" s="3">
         <v>194000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="N83" s="3">
         <v>90300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="O83" s="3">
         <v>89700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="P83" s="3">
         <v>176700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="Q83" s="3">
         <v>177000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="R83" s="3">
         <v>99300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="S83" s="3">
         <v>99500</v>
       </c>
     </row>
-    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3508,8 +4315,20 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3549,8 +4368,20 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3590,8 +4421,20 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3631,8 +4474,20 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3672,49 +4527,73 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>501300</v>
+      </c>
+      <c r="E89" s="3">
+        <v>501400</v>
+      </c>
+      <c r="F89" s="3">
+        <v>346400</v>
+      </c>
+      <c r="G89" s="3">
+        <v>346600</v>
+      </c>
+      <c r="H89" s="3">
         <v>412800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="I89" s="3">
         <v>416500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="J89" s="3">
         <v>663800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="K89" s="3">
         <v>663600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="L89" s="3">
         <v>523700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="M89" s="3">
         <v>522600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="N89" s="3">
         <v>469000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="O89" s="3">
         <v>467800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="P89" s="3">
         <v>246900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="Q89" s="3">
         <v>246500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="R89" s="3">
         <v>191200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="S89" s="3">
         <v>189900</v>
       </c>
     </row>
-    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3730,49 +4609,65 @@
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
-    </row>
-    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-752600</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-752800</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-793400</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-793600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-624100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="I91" s="3">
         <v>-629700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="J91" s="3">
         <v>-792900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="K91" s="3">
         <v>-792700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="L91" s="3">
         <v>-492500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="M91" s="3">
         <v>-491400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="N91" s="3">
         <v>-456700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="O91" s="3">
         <v>-455600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="P91" s="3">
         <v>-331700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="Q91" s="3">
         <v>-331100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="R91" s="3">
         <v>-971600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="S91" s="3">
         <v>-965000</v>
       </c>
     </row>
-    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3812,8 +4707,20 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3853,49 +4760,73 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3888400</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3889400</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-653200</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-653500</v>
+      </c>
+      <c r="H94" s="3">
         <v>-407800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="I94" s="3">
         <v>-411500</v>
       </c>
-      <c r="F94" s="3">
-        <v>-697900</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
+        <v>-704000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-697700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="L94" s="3">
         <v>-597500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="M94" s="3">
         <v>-596200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="N94" s="3">
         <v>-422000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="O94" s="3">
         <v>-421000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="P94" s="3">
         <v>-72200</v>
       </c>
-      <c r="M94" s="3">
+      <c r="Q94" s="3">
         <v>-72000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="R94" s="3">
         <v>-252200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="S94" s="3">
         <v>-250500</v>
       </c>
     </row>
-    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3911,49 +4842,65 @@
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
-    </row>
-    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>392700</v>
+      </c>
+      <c r="E96" s="3">
+        <v>392800</v>
+      </c>
+      <c r="F96" s="3">
+        <v>207200</v>
+      </c>
+      <c r="G96" s="3">
+        <v>207300</v>
+      </c>
+      <c r="H96" s="3">
         <v>352900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="I96" s="3">
         <v>356100</v>
       </c>
-      <c r="F96" s="3">
+      <c r="J96" s="3">
         <v>511500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="K96" s="3">
         <v>511400</v>
       </c>
-      <c r="H96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="M96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N96" s="3">
         <v>486100</v>
       </c>
-      <c r="K96" s="3">
+      <c r="O96" s="3">
         <v>484900</v>
       </c>
-      <c r="L96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="M96" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q96" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R96" s="3">
         <v>549000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="S96" s="3">
         <v>545400</v>
       </c>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3993,8 +4940,20 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4034,8 +4993,20 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4075,127 +5046,175 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>4829100</v>
+      </c>
+      <c r="E100" s="3">
+        <v>4830300</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-509600</v>
+      </c>
+      <c r="G100" s="3">
+        <v>-509800</v>
+      </c>
+      <c r="H100" s="3">
         <v>1837200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="I100" s="3">
         <v>1853700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="J100" s="3">
         <v>-125900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="K100" s="3">
         <v>-125900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="L100" s="3">
         <v>669700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="M100" s="3">
         <v>668200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="N100" s="3">
         <v>-190400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="O100" s="3">
         <v>-189900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="P100" s="3">
         <v>309300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="Q100" s="3">
         <v>308700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="R100" s="3">
         <v>-6400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="S100" s="3">
         <v>-6400</v>
       </c>
     </row>
-    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>32300</v>
+      </c>
+      <c r="F101" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="G101" s="3">
+        <v>-16000</v>
+      </c>
+      <c r="H101" s="3">
         <v>-13900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="I101" s="3">
         <v>-13900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="J101" s="3">
         <v>12300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="K101" s="3">
         <v>12300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="L101" s="3">
         <v>-7000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="M101" s="3">
         <v>-7000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="N101" s="3">
         <v>-15100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="O101" s="3">
         <v>-15000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="P101" s="3">
         <v>-30300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="Q101" s="3">
         <v>-30300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="R101" s="3">
         <v>-5100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="S101" s="3">
         <v>-5100</v>
       </c>
     </row>
-    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1463600</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1464000</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-812800</v>
+      </c>
+      <c r="G102" s="3">
+        <v>-813100</v>
+      </c>
+      <c r="H102" s="3">
         <v>1874200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="I102" s="3">
         <v>1891000</v>
       </c>
-      <c r="F102" s="3">
-        <v>-176100</v>
-      </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
+        <v>-182100</v>
+      </c>
+      <c r="K102" s="3">
         <v>-176000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="L102" s="3">
         <v>582100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="M102" s="3">
         <v>580800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="N102" s="3">
         <v>-131100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="O102" s="3">
         <v>-130800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="P102" s="3">
         <v>477000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="Q102" s="3">
         <v>476200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="R102" s="3">
         <v>-82500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="S102" s="3">
         <v>-81900</v>
       </c>
     </row>
